--- a/data/trans_bre/P16A01-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P16A01-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 2,25</t>
+          <t>-3,63; 2,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 7,39</t>
+          <t>-1,33; 7,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,64; 9,28</t>
+          <t>1,36; 9,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 8,98</t>
+          <t>-2,26; 9,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-44,84; 42,39</t>
+          <t>-41,43; 48,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,87; 105,07</t>
+          <t>-11,65; 101,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,41; 214,21</t>
+          <t>14,85; 224,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-37,23; 439,43</t>
+          <t>-40,13; 381,47</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 5,81</t>
+          <t>0,28; 5,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 3,52</t>
+          <t>-3,62; 3,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 2,65</t>
+          <t>-3,96; 2,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,32; 0,43</t>
+          <t>-10,01; 0,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,96; 154,14</t>
+          <t>4,44; 147,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-31,36; 43,5</t>
+          <t>-33,76; 43,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-35,48; 37,52</t>
+          <t>-36,86; 36,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-66,13; 4,19</t>
+          <t>-66,85; 1,62</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 4,25</t>
+          <t>-1,78; 3,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 1,91</t>
+          <t>-4,29; 1,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 3,7</t>
+          <t>-2,15; 3,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 1,97</t>
+          <t>-3,86; 2,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-21,06; 87,56</t>
+          <t>-24,68; 79,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-40,63; 26,89</t>
+          <t>-40,93; 27,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-26,17; 62,58</t>
+          <t>-25,3; 64,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-40,55; 33,05</t>
+          <t>-41,45; 38,35</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 1,84</t>
+          <t>-3,77; 1,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 2,83</t>
+          <t>-3,58; 2,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 3,32</t>
+          <t>-2,43; 3,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 5,54</t>
+          <t>-1,13; 5,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-56,51; 52,37</t>
+          <t>-54,42; 56,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-37,73; 47,71</t>
+          <t>-38,67; 47,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-30,78; 69,4</t>
+          <t>-31,48; 73,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-14,85; 241,18</t>
+          <t>-17,08; 232,1</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 1,93</t>
+          <t>-4,75; 1,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 0,66</t>
+          <t>-6,87; 0,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 4,12</t>
+          <t>-3,05; 4,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 5,75</t>
+          <t>0,26; 5,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-54,25; 43,99</t>
+          <t>-56,28; 35,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-60,27; 11,24</t>
+          <t>-59,95; 11,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-33,42; 67,76</t>
+          <t>-30,71; 76,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,52; 129,8</t>
+          <t>3,26; 121,48</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 3,16</t>
+          <t>-6,16; 2,76</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 1,06</t>
+          <t>-7,68; 1,52</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 3,84</t>
+          <t>-4,11; 3,57</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 0,79</t>
+          <t>-7,72; 0,94</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-48,39; 47,02</t>
+          <t>-48,18; 39,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-60,96; 17,15</t>
+          <t>-58,44; 19,89</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-41,86; 64,22</t>
+          <t>-44,1; 66,9</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-76,13; 10,98</t>
+          <t>-74,84; 13,09</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-17,8; -6,35</t>
+          <t>-18,21; -6,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-12,86; -1,24</t>
+          <t>-12,89; -0,96</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,44; 1,75</t>
+          <t>-7,85; 2,19</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,05; 5,72</t>
+          <t>-0,13; 5,52</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-84,2; -45,83</t>
+          <t>-84,43; -48,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-62,73; -7,73</t>
+          <t>-64,13; -7,42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-55,39; 20,94</t>
+          <t>-54,82; 24,92</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,57; 146,26</t>
+          <t>-2,32; 128,02</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 0,73</t>
+          <t>-1,73; 0,7</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 0,27</t>
+          <t>-2,67; 0,33</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,97</t>
+          <t>-0,7; 1,98</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 2,22</t>
+          <t>-1,03; 2,37</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-23,42; 11,55</t>
+          <t>-23,63; 10,64</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-25,51; 3,53</t>
+          <t>-25,74; 4,07</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 28,1</t>
+          <t>-8,72; 28,16</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-14,76; 40,2</t>
+          <t>-13,69; 43,19</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A01-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P16A01-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,21</t>
+          <t>2,18</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>36,56%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 2,76</t>
+          <t>-4,22; 2,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 7,17</t>
+          <t>-1,07; 7,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 9,55</t>
+          <t>1,72; 9,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 9,54</t>
+          <t>-3,27; 8,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-41,43; 48,8</t>
+          <t>-48,21; 37,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 101,79</t>
+          <t>-10,62; 109,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,85; 224,9</t>
+          <t>19,04; 210,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-40,13; 381,47</t>
+          <t>-41,5; 301,17</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-4,31</t>
+          <t>-3,7</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-38,28%</t>
+          <t>-33,59%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 5,35</t>
+          <t>0,35; 5,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 3,24</t>
+          <t>-3,6; 2,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 2,59</t>
+          <t>-3,75; 2,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,01; 0,02</t>
+          <t>-8,77; 0,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,44; 147,95</t>
+          <t>2,65; 159,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-33,76; 43,14</t>
+          <t>-32,31; 36,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-36,86; 36,89</t>
+          <t>-35,02; 41,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-66,85; 1,62</t>
+          <t>-59,46; 5,69</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,79</t>
+          <t>-0,73</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-10,46%</t>
+          <t>-9,85%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 3,98</t>
+          <t>-1,36; 4,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 1,81</t>
+          <t>-4,2; 2,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 3,55</t>
+          <t>-2,13; 3,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 2,22</t>
+          <t>-3,76; 1,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-24,68; 79,1</t>
+          <t>-18,48; 96,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-40,93; 27,38</t>
+          <t>-41,73; 32,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-25,3; 64,45</t>
+          <t>-24,36; 60,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-41,45; 38,35</t>
+          <t>-40,58; 33,25</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,66</t>
+          <t>0,11</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 1,88</t>
+          <t>-3,62; 1,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 2,75</t>
+          <t>-3,7; 3,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 3,55</t>
+          <t>-2,0; 3,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 5,15</t>
+          <t>-2,19; 2,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-54,42; 56,71</t>
+          <t>-53,99; 50,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-38,67; 47,93</t>
+          <t>-38,27; 54,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-31,48; 73,32</t>
+          <t>-25,64; 74,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-17,08; 232,1</t>
+          <t>-26,89; 51,72</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,18</t>
+          <t>3,37</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>58,84%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 1,65</t>
+          <t>-5,13; 1,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 0,7</t>
+          <t>-7,3; 0,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 4,46</t>
+          <t>-3,06; 4,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,26; 5,71</t>
+          <t>0,77; 5,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-56,28; 35,33</t>
+          <t>-58,45; 36,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-59,95; 11,38</t>
+          <t>-62,05; 5,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-30,71; 76,42</t>
+          <t>-33,02; 71,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,26; 121,48</t>
+          <t>9,14; 133,28</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-2,87</t>
+          <t>0,12</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-35,37%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 2,76</t>
+          <t>-6,24; 2,87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,68; 1,52</t>
+          <t>-7,65; 1,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 3,57</t>
+          <t>-4,02; 3,73</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 0,94</t>
+          <t>-3,23; 2,77</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-48,18; 39,55</t>
+          <t>-48,77; 43,16</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-58,44; 19,89</t>
+          <t>-58,37; 18,96</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-44,1; 66,9</t>
+          <t>-42,66; 66,6</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-74,84; 13,09</t>
+          <t>-31,89; 44,11</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,03</t>
+          <t>3,11</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>54,8%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-18,21; -6,69</t>
+          <t>-17,97; -6,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-12,89; -0,96</t>
+          <t>-12,48; -1,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 2,19</t>
+          <t>-8,41; 1,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 5,52</t>
+          <t>0,23; 5,92</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-84,43; -48,16</t>
+          <t>-85,37; -49,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-64,13; -7,42</t>
+          <t>-62,49; -6,97</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-54,82; 24,92</t>
+          <t>-55,88; 21,49</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 128,02</t>
+          <t>1,54; 145,12</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 0,7</t>
+          <t>-1,73; 0,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 0,33</t>
+          <t>-2,57; 0,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 1,98</t>
+          <t>-0,78; 1,98</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 2,37</t>
+          <t>-0,74; 1,82</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-23,63; 10,64</t>
+          <t>-22,35; 11,24</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-25,74; 4,07</t>
+          <t>-25,06; 3,2</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 28,16</t>
+          <t>-8,98; 28,57</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-13,69; 43,19</t>
+          <t>-9,44; 29,68</t>
         </is>
       </c>
     </row>
